--- a/data/processed/pipeline_report.xlsx
+++ b/data/processed/pipeline_report.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
